--- a/services_forms/005_tip_payment_form--services_forms.xlsx
+++ b/services_forms/005_tip_payment_form--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'10',_'label':_'10%'}</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': '10', 'label': '10%'}</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'15%',_'label':_'15%'}</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': '15%', 'label': '15%'}</t>
+          <t>15%</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'20%',_'label':_'20%'}</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': '20%', 'label': '20%'}</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'base_price',_'label':_'base_price'}</t>
+          <t>base_price</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'base price', 'label': 'Base Price'}</t>
+          <t>Base Price</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'tip_percentage',_'label':_'tip_percentage'}</t>
+          <t>tip_percentage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'tip percentage', 'label': 'Tip Percentage'}</t>
+          <t>Tip Percentage</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'tip_amount',_'label':_'tip_amount'}</t>
+          <t>tip_amount</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'tip amount', 'label': 'Tip Amount'}</t>
+          <t>Tip Amount</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'calculate_tip',_'label':_'calculate_tip'}</t>
+          <t>calculate_tip</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'calculate tip', 'label': 'Calculate Tip'}</t>
+          <t>Calculate Tip</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'reset',_'label':_'reset'}</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'reset', 'label': 'Reset'}</t>
+          <t>Reset</t>
         </is>
       </c>
     </row>
